--- a/templates_4color/fourcolor_template.xlsx
+++ b/templates_4color/fourcolor_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LBTECH\Downloads\สำหรับรันบน github\streamlit-procurement-app-main\templates_4color\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project_AutoDocs normal - Copy\templates_4color\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4D228C9-91CA-43AD-BFA1-6D8C746A0F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34E5BE9-B7A4-4780-8313-F8E0934C7A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{B5833F3F-2512-405C-A06E-47F8F2F5C921}"/>
   </bookViews>
@@ -97,9 +97,6 @@
     <t>ประเภทเงิน</t>
   </si>
   <si>
-    <t>ปีงบประมาณ 2569</t>
-  </si>
-  <si>
     <t>งานพัสดุกลาง</t>
   </si>
   <si>
@@ -239,6 +236,9 @@
   </si>
   <si>
     <t>{{RECEIVER_NO}}</t>
+  </si>
+  <si>
+    <t>ปีงบประมาณ 2570</t>
   </si>
 </sst>
 </file>
@@ -611,7 +611,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -638,14 +638,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -794,6 +789,14 @@
     </xf>
     <xf numFmtId="187" fontId="3" fillId="0" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1529,570 +1532,570 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="41" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B1" s="44" t="s">
+    <row r="1" spans="1:11" s="38" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B1" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="125" t="s">
+      <c r="C1" s="126" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="42" t="s">
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="39" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="126" t="s">
+      <c r="A2" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="126" t="s">
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="127" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="129"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="130"/>
     </row>
     <row r="3" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="16" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="14"/>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="39"/>
-      <c r="E3" s="126" t="s">
+      <c r="D3" s="36"/>
+      <c r="E3" s="127" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="128"/>
-      <c r="G3" s="107" t="s">
+      <c r="F3" s="129"/>
+      <c r="G3" s="108" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="108"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="108"/>
-      <c r="K3" s="109"/>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="109"/>
+      <c r="K3" s="110"/>
     </row>
     <row r="4" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="81" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="82"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="126" t="s">
+      <c r="A4" s="82" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="83"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="127" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="127"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="93"/>
-      <c r="K4" s="97"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="98"/>
     </row>
     <row r="5" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="16" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="14"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="98" t="s">
+      <c r="C5" s="34"/>
+      <c r="D5" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="99"/>
-      <c r="F5" s="99"/>
-      <c r="G5" s="107" t="s">
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="108" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="108"/>
-      <c r="I5" s="130" t="s">
+      <c r="H5" s="109"/>
+      <c r="I5" s="131" t="s">
+        <v>65</v>
+      </c>
+      <c r="J5" s="131"/>
+      <c r="K5" s="132"/>
+    </row>
+    <row r="6" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="130"/>
-      <c r="K5" s="131"/>
-    </row>
-    <row r="6" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="94" t="s">
+      <c r="B6" s="96"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="82" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="84"/>
+    </row>
+    <row r="7" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="99" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="92"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="97"/>
-      <c r="G6" s="81" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="82"/>
-      <c r="K6" s="83"/>
-    </row>
-    <row r="7" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="98" t="s">
+      <c r="B7" s="100"/>
+      <c r="C7" s="101"/>
+      <c r="D7" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="99"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="29" t="s">
+      <c r="E7" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="F7" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="G7" s="108" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="107" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="108"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="108"/>
-      <c r="K7" s="109"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="109"/>
+      <c r="J7" s="109"/>
+      <c r="K7" s="110"/>
     </row>
     <row r="8" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="7"/>
       <c r="B8" s="4"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="F8" s="32"/>
+      <c r="G8" s="115" t="s">
+        <v>58</v>
+      </c>
+      <c r="H8" s="116"/>
+      <c r="I8" s="116"/>
+      <c r="J8" s="116"/>
+      <c r="K8" s="117"/>
+    </row>
+    <row r="9" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="35"/>
-      <c r="G8" s="114" t="s">
-        <v>59</v>
-      </c>
-      <c r="H8" s="115"/>
-      <c r="I8" s="115"/>
-      <c r="J8" s="115"/>
-      <c r="K8" s="116"/>
-    </row>
-    <row r="9" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="34" t="s">
+      <c r="B9" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="101" t="s">
+      <c r="C9" s="104" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="104" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="103" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="103" t="s">
+      <c r="E9" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="34" t="s">
+      <c r="F9" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="34" t="s">
+      <c r="G9" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="H9" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="110" t="s">
+      <c r="I9" s="112"/>
+      <c r="J9" s="106" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="111"/>
-      <c r="J9" s="105" t="s">
+      <c r="K9" s="102"/>
+    </row>
+    <row r="10" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="K9" s="101"/>
-    </row>
-    <row r="10" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="45" t="s">
+      <c r="B10" s="103"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="105"/>
+      <c r="E10" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="102"/>
-      <c r="C10" s="104"/>
-      <c r="D10" s="104"/>
-      <c r="E10" s="45" t="s">
+      <c r="F10" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="45" t="s">
+      <c r="G10" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="33" t="s">
+      <c r="H10" s="113" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="112" t="s">
+      <c r="I10" s="114"/>
+      <c r="J10" s="107"/>
+      <c r="K10" s="103"/>
+    </row>
+    <row r="11" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="48" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="28"/>
+      <c r="C11" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="I10" s="113"/>
-      <c r="J10" s="106"/>
-      <c r="K10" s="102"/>
-    </row>
-    <row r="11" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="69" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="32" t="s">
+      <c r="E11" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" s="52"/>
+      <c r="H11" s="70" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" s="15"/>
+      <c r="J11" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="K11" s="25"/>
+    </row>
+    <row r="12" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="23"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="75"/>
+      <c r="K12" s="19"/>
+    </row>
+    <row r="13" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="23"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="75"/>
+      <c r="K13" s="19"/>
+    </row>
+    <row r="14" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="23"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="50"/>
+      <c r="J14" s="75"/>
+      <c r="K14" s="19"/>
+    </row>
+    <row r="15" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="23"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="75"/>
+      <c r="K15" s="19"/>
+    </row>
+    <row r="16" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="23"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="67"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="75"/>
+      <c r="K16" s="19"/>
+    </row>
+    <row r="17" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="23"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="50"/>
+      <c r="J17" s="75"/>
+      <c r="K17" s="19"/>
+    </row>
+    <row r="18" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="23"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="75"/>
+      <c r="K18" s="19"/>
+    </row>
+    <row r="19" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="23"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="75"/>
+      <c r="K19" s="19"/>
+    </row>
+    <row r="20" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="23"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="75"/>
+      <c r="K20" s="19"/>
+    </row>
+    <row r="21" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="23"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="75"/>
+      <c r="K21" s="19"/>
+    </row>
+    <row r="22" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="23"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="75"/>
+      <c r="K22" s="19"/>
+    </row>
+    <row r="23" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="23"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="75"/>
+      <c r="K23" s="19"/>
+    </row>
+    <row r="24" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="23"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="75"/>
+      <c r="K24" s="19"/>
+    </row>
+    <row r="25" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="23"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="75"/>
+      <c r="K25" s="19"/>
+    </row>
+    <row r="26" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="23"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="50"/>
+      <c r="J26" s="75"/>
+      <c r="K26" s="19"/>
+    </row>
+    <row r="27" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="23"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="50"/>
+      <c r="J27" s="75"/>
+      <c r="K27" s="19"/>
+    </row>
+    <row r="28" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="44"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="44"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="72"/>
+      <c r="I28" s="51"/>
+      <c r="J28" s="76"/>
+      <c r="K28" s="53"/>
+    </row>
+    <row r="29" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="55"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="69"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="60"/>
+      <c r="J29" s="77"/>
+      <c r="K29" s="61"/>
+    </row>
+    <row r="30" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="G11" s="55"/>
-      <c r="H11" s="73" t="s">
-        <v>62</v>
-      </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="77" t="s">
-        <v>63</v>
-      </c>
-      <c r="K11" s="28"/>
-    </row>
-    <row r="12" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="22"/>
-    </row>
-    <row r="13" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="78"/>
-      <c r="K13" s="22"/>
-    </row>
-    <row r="14" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="74"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="78"/>
-      <c r="K14" s="22"/>
-    </row>
-    <row r="15" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="74"/>
-      <c r="I15" s="53"/>
-      <c r="J15" s="78"/>
-      <c r="K15" s="22"/>
-    </row>
-    <row r="16" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="70"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="74"/>
-      <c r="I16" s="53"/>
-      <c r="J16" s="78"/>
-      <c r="K16" s="22"/>
-    </row>
-    <row r="17" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="52"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="74"/>
-      <c r="I17" s="53"/>
-      <c r="J17" s="78"/>
-      <c r="K17" s="22"/>
-    </row>
-    <row r="18" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="26"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="74"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="78"/>
-      <c r="K18" s="22"/>
-    </row>
-    <row r="19" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="26"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="78"/>
-      <c r="K19" s="22"/>
-    </row>
-    <row r="20" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="78"/>
-      <c r="K20" s="22"/>
-    </row>
-    <row r="21" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="78"/>
-      <c r="K21" s="22"/>
-    </row>
-    <row r="22" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="26"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="70"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="74"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="78"/>
-      <c r="K22" s="22"/>
-    </row>
-    <row r="23" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="70"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="74"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="78"/>
-      <c r="K23" s="22"/>
-    </row>
-    <row r="24" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="26"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="74"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="78"/>
-      <c r="K24" s="22"/>
-    </row>
-    <row r="25" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="26"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="52"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="74"/>
-      <c r="I25" s="53"/>
-      <c r="J25" s="78"/>
-      <c r="K25" s="22"/>
-    </row>
-    <row r="26" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="26"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="74"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="78"/>
-      <c r="K26" s="22"/>
-    </row>
-    <row r="27" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="26"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="74"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="78"/>
-      <c r="K27" s="22"/>
-    </row>
-    <row r="28" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="47"/>
-      <c r="B28" s="46"/>
-      <c r="C28" s="71"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="49"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="75"/>
-      <c r="I28" s="54"/>
-      <c r="J28" s="79"/>
-      <c r="K28" s="56"/>
-    </row>
-    <row r="29" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="58"/>
-      <c r="B29" s="59"/>
-      <c r="C29" s="72"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="60"/>
-      <c r="F29" s="61"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="76"/>
-      <c r="I29" s="63"/>
-      <c r="J29" s="80"/>
-      <c r="K29" s="64"/>
-    </row>
-    <row r="30" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="84" t="s">
+      <c r="B30" s="86"/>
+      <c r="C30" s="87"/>
+      <c r="D30" s="64"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="118"/>
+      <c r="G30" s="118"/>
+      <c r="H30" s="118"/>
+      <c r="I30" s="119"/>
+      <c r="J30" s="80"/>
+      <c r="K30" s="81"/>
+    </row>
+    <row r="31" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="88"/>
+      <c r="B31" s="89"/>
+      <c r="C31" s="90"/>
+      <c r="D31" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="85"/>
-      <c r="C30" s="86"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="117"/>
-      <c r="G30" s="117"/>
-      <c r="H30" s="117"/>
-      <c r="I30" s="118"/>
-      <c r="J30" s="21"/>
-      <c r="K30" s="20"/>
-    </row>
-    <row r="31" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="87"/>
-      <c r="B31" s="88"/>
-      <c r="C31" s="89"/>
-      <c r="D31" s="65" t="s">
-        <v>42</v>
-      </c>
-      <c r="E31" s="66"/>
-      <c r="F31" s="119"/>
-      <c r="G31" s="119"/>
-      <c r="H31" s="119"/>
-      <c r="I31" s="120"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="18"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="120"/>
+      <c r="G31" s="120"/>
+      <c r="H31" s="120"/>
+      <c r="I31" s="121"/>
+      <c r="J31" s="78"/>
+      <c r="K31" s="79"/>
     </row>
     <row r="32" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="54"/>
+      <c r="C32" s="54"/>
+      <c r="D32" s="16" t="s">
         <v>43</v>
-      </c>
-      <c r="B32" s="57"/>
-      <c r="C32" s="57"/>
-      <c r="D32" s="16" t="s">
-        <v>44</v>
       </c>
       <c r="E32" s="14"/>
       <c r="F32" s="15"/>
       <c r="G32" s="14"/>
-      <c r="H32" s="123" t="s">
+      <c r="H32" s="124" t="s">
         <v>1</v>
       </c>
-      <c r="I32" s="123"/>
-      <c r="J32" s="123"/>
-      <c r="K32" s="124"/>
+      <c r="I32" s="124"/>
+      <c r="J32" s="124"/>
+      <c r="K32" s="125"/>
     </row>
     <row r="33" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="10"/>
       <c r="D33" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" s="14"/>
+      <c r="F33" s="122" t="s">
         <v>45</v>
       </c>
-      <c r="E33" s="14"/>
-      <c r="F33" s="121" t="s">
+      <c r="G33" s="122"/>
+      <c r="H33" s="122"/>
+      <c r="I33" s="122"/>
+      <c r="J33" s="122"/>
+      <c r="K33" s="123"/>
+    </row>
+    <row r="34" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="93" t="s">
         <v>46</v>
       </c>
-      <c r="G33" s="121"/>
-      <c r="H33" s="121"/>
-      <c r="I33" s="121"/>
-      <c r="J33" s="121"/>
-      <c r="K33" s="122"/>
-    </row>
-    <row r="34" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="92" t="s">
+      <c r="B34" s="94"/>
+      <c r="C34" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D34" s="16" t="s">
         <v>47</v>
-      </c>
-      <c r="B34" s="93"/>
-      <c r="C34" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>48</v>
       </c>
       <c r="E34" s="14"/>
       <c r="G34" s="17"/>
-      <c r="H34" s="121" t="s">
-        <v>49</v>
-      </c>
-      <c r="I34" s="121"/>
-      <c r="J34" s="121"/>
-      <c r="K34" s="122"/>
+      <c r="H34" s="122" t="s">
+        <v>48</v>
+      </c>
+      <c r="I34" s="122"/>
+      <c r="J34" s="122"/>
+      <c r="K34" s="123"/>
     </row>
     <row r="35" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
       <c r="D35" s="16"/>
       <c r="E35" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F35" s="15"/>
       <c r="G35" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H35" s="14"/>
       <c r="I35" s="13"/>
@@ -2101,11 +2104,11 @@
     </row>
     <row r="36" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D36" s="10"/>
       <c r="G36" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I36" s="9"/>
       <c r="K36" s="8"/>
@@ -2114,27 +2117,27 @@
       <c r="A37" s="10"/>
       <c r="D37" s="10"/>
       <c r="E37" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="I37" s="9"/>
       <c r="K37" s="8"/>
     </row>
     <row r="38" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="90" t="s">
-        <v>57</v>
-      </c>
-      <c r="B38" s="91"/>
+      <c r="A38" s="91" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="92"/>
       <c r="C38" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D38" s="7"/>
       <c r="E38" s="4"/>
       <c r="F38" s="6"/>
       <c r="G38" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H38" s="4"/>
       <c r="I38" s="5"/>
